--- a/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N66_analysis.xlsx
+++ b/dataset_t6_grouped/results2/G1/G1_T7394_W0022F0001T0006Z000C1N66_analysis.xlsx
@@ -480,16 +480,16 @@
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>71.02708340173329</v>
+        <v>11.54190105278166</v>
       </c>
       <c r="D2" t="n">
-        <v>67.74001584663213</v>
+        <v>11.00775257507772</v>
       </c>
       <c r="E2" t="n">
-        <v>20.95981023780704</v>
+        <v>3.405969163643645</v>
       </c>
       <c r="F2" t="n">
-        <v>19.01319559430024</v>
+        <v>3.089644284073789</v>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -512,16 +512,16 @@
         <v>2</v>
       </c>
       <c r="C3" t="n">
-        <v>69.09228859366264</v>
+        <v>11.22749689647018</v>
       </c>
       <c r="D3" t="n">
-        <v>57.97055301287615</v>
+        <v>9.420214864592374</v>
       </c>
       <c r="E3" t="n">
-        <v>20.95981023780704</v>
+        <v>3.405969163643645</v>
       </c>
       <c r="F3" t="n">
-        <v>19.01319559430024</v>
+        <v>3.089644284073789</v>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -544,16 +544,16 @@
         <v>3</v>
       </c>
       <c r="C4" t="n">
-        <v>47.77999063720399</v>
+        <v>7.764248478545648</v>
       </c>
       <c r="D4" t="n">
-        <v>35.04092741571228</v>
+        <v>5.694150705053245</v>
       </c>
       <c r="E4" t="n">
-        <v>20.95981023780704</v>
+        <v>3.405969163643645</v>
       </c>
       <c r="F4" t="n">
-        <v>19.01319559430024</v>
+        <v>3.089644284073789</v>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -576,16 +576,16 @@
         <v>4</v>
       </c>
       <c r="C5" t="n">
-        <v>19.05239656902619</v>
+        <v>3.096014442466756</v>
       </c>
       <c r="D5" t="n">
-        <v>19.28074663164364</v>
+        <v>3.133121327642091</v>
       </c>
       <c r="E5" t="n">
-        <v>20.95981023780704</v>
+        <v>3.405969163643645</v>
       </c>
       <c r="F5" t="n">
-        <v>19.01319559430024</v>
+        <v>3.089644284073789</v>
       </c>
       <c r="G5" t="inlineStr">
         <is>
